--- a/Keras_Torch/KerasModels.xlsx
+++ b/Keras_Torch/KerasModels.xlsx
@@ -4,12 +4,25 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19635" windowHeight="7695"/>
+    <workbookView windowWidth="20745" windowHeight="9675"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -162,6 +175,21 @@
     </r>
   </si>
   <si>
+    <t>EfficientNetV2L</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>119.0M</t>
+    </r>
+  </si>
+  <si>
     <t>ConvNeXtBase</t>
   </si>
   <si>
@@ -177,6 +205,111 @@
     </r>
   </si>
   <si>
+    <t>EfficientNetV2M</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>54.4M</t>
+    </r>
+  </si>
+  <si>
+    <t>EfficientNetB7</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>66.7M</t>
+    </r>
+  </si>
+  <si>
+    <t>EfficientNetB6</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>43.3M</t>
+    </r>
+  </si>
+  <si>
+    <t>EfficientNetV2S</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>21.6M</t>
+    </r>
+  </si>
+  <si>
+    <t>EfficientNetB5</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>30.6M</t>
+    </r>
+  </si>
+  <si>
+    <t>EfficientNetB4</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>19.5M</t>
+    </r>
+  </si>
+  <si>
+    <t>NASNetLarge</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>88.9M</t>
+    </r>
+  </si>
+  <si>
     <t>ConvNeXtSmall</t>
   </si>
   <si>
@@ -192,6 +325,36 @@
     </r>
   </si>
   <si>
+    <t>EfficientNetV2B3</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>14.5M</t>
+    </r>
+  </si>
+  <si>
+    <t>EfficientNetB3</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>12.3M</t>
+    </r>
+  </si>
+  <si>
     <t>ConvNeXtTiny</t>
   </si>
   <si>
@@ -207,66 +370,6 @@
     </r>
   </si>
   <si>
-    <t>EfficientNetV2L</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>119.0M</t>
-    </r>
-  </si>
-  <si>
-    <t>EfficientNetV2M</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>54.4M</t>
-    </r>
-  </si>
-  <si>
-    <t>EfficientNetV2S</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>21.6M</t>
-    </r>
-  </si>
-  <si>
-    <t>EfficientNetV2B3</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>14.5M</t>
-    </r>
-  </si>
-  <si>
     <t>EfficientNetV2B2</t>
   </si>
   <si>
@@ -282,6 +385,36 @@
     </r>
   </si>
   <si>
+    <t>InceptionResNetV2</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>55.9M</t>
+    </r>
+  </si>
+  <si>
+    <t>EfficientNetB2</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>9.2M</t>
+    </r>
+  </si>
+  <si>
     <t>EfficientNetV2B1</t>
   </si>
   <si>
@@ -297,6 +430,36 @@
     </r>
   </si>
   <si>
+    <t>EfficientNetB1</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>7.9M</t>
+    </r>
+  </si>
+  <si>
+    <t>Xception</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>22.9M</t>
+    </r>
+  </si>
+  <si>
     <t>EfficientNetV2B0</t>
   </si>
   <si>
@@ -312,157 +475,85 @@
     </r>
   </si>
   <si>
-    <t>EfficientNetB7</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>66.7M</t>
-    </r>
-  </si>
-  <si>
-    <t>EfficientNetB6</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>43.3M</t>
-    </r>
-  </si>
-  <si>
-    <t>EfficientNetB5</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>30.6M</t>
-    </r>
-  </si>
-  <si>
-    <t>NASNetLarge</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>88.9M</t>
-    </r>
-  </si>
-  <si>
-    <t>EfficientNetB4</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>19.5M</t>
-    </r>
-  </si>
-  <si>
-    <t>EfficientNetB3</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>12.3M</t>
-    </r>
-  </si>
-  <si>
-    <t>InceptionResNetV2</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>55.9M</t>
+    <t>ResNet152V2</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>60.4M</t>
+    </r>
+  </si>
+  <si>
+    <t>InceptionV3</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>23.9M</t>
+    </r>
+  </si>
+  <si>
+    <t>DenseNet201</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>20.2M</t>
+    </r>
+  </si>
+  <si>
+    <t>ResNet101V2</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>44.7M</t>
+    </r>
+  </si>
+  <si>
+    <t>EfficientNetB0</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5.3M</t>
     </r>
   </si>
   <si>
     <t>ResNet152</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>60.4M</t>
-    </r>
-  </si>
-  <si>
-    <t>DenseNet201</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>20.2M</t>
-    </r>
-  </si>
-  <si>
-    <t>Xception</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>22.9M</t>
-    </r>
-  </si>
-  <si>
-    <t>ResNet152V2</t>
+    <t>ResNet101</t>
   </si>
   <si>
     <t>DenseNet169</t>
@@ -480,19 +571,40 @@
     </r>
   </si>
   <si>
-    <t>ResNet101</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>44.7M</t>
-    </r>
+    <t>ResNet50V2</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>25.6M</t>
+    </r>
+  </si>
+  <si>
+    <t>DenseNet121</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>8.1M</t>
+    </r>
+  </si>
+  <si>
+    <t>ResNet50</t>
+  </si>
+  <si>
+    <t>NASNetMobile</t>
   </si>
   <si>
     <t>VGG19</t>
@@ -510,39 +622,6 @@
     </r>
   </si>
   <si>
-    <t>EfficientNetB2</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>9.2M</t>
-    </r>
-  </si>
-  <si>
-    <t>DenseNet121</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>8.1M</t>
-    </r>
-  </si>
-  <si>
-    <t>ResNet101V2</t>
-  </si>
-  <si>
     <t>VGG16</t>
   </si>
   <si>
@@ -556,72 +635,6 @@
       </rPr>
       <t>138.4M</t>
     </r>
-  </si>
-  <si>
-    <t>EfficientNetB1</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>7.9M</t>
-    </r>
-  </si>
-  <si>
-    <t>ResNet50</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>25.6M</t>
-    </r>
-  </si>
-  <si>
-    <t>EfficientNetB0</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>5.3M</t>
-    </r>
-  </si>
-  <si>
-    <t>ResNet50V2</t>
-  </si>
-  <si>
-    <t>InceptionV3</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>23.9M</t>
-    </r>
-  </si>
-  <si>
-    <t>NASNetMobile</t>
   </si>
   <si>
     <t>MobileNetV2</t>
@@ -657,7 +670,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -1461,7 +1474,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1487,18 +1500,6 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2163,13 +2164,13 @@
         <v>13</v>
       </c>
       <c r="B4" s="10">
-        <v>338.58</v>
+        <v>479</v>
       </c>
       <c r="C4" s="11">
-        <v>0.853</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>9</v>
+        <v>0.857</v>
+      </c>
+      <c r="D4" s="11">
+        <v>0.975</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>14</v>
@@ -2189,10 +2190,10 @@
         <v>15</v>
       </c>
       <c r="B5" s="10">
-        <v>192.29</v>
+        <v>338.58</v>
       </c>
       <c r="C5" s="11">
-        <v>0.823</v>
+        <v>0.853</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>9</v>
@@ -2215,13 +2216,13 @@
         <v>17</v>
       </c>
       <c r="B6" s="10">
-        <v>109.42</v>
+        <v>220</v>
       </c>
       <c r="C6" s="11">
-        <v>0.813</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>9</v>
+        <v>0.853</v>
+      </c>
+      <c r="D6" s="11">
+        <v>0.974</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>18</v>
@@ -2241,25 +2242,25 @@
         <v>19</v>
       </c>
       <c r="B7" s="10">
-        <v>479</v>
+        <v>256</v>
       </c>
       <c r="C7" s="11">
-        <v>0.857</v>
+        <v>0.843</v>
       </c>
       <c r="D7" s="11">
-        <v>0.975</v>
+        <v>0.97</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="H7" s="12" t="s">
-        <v>9</v>
+      <c r="F7" s="10">
+        <v>438</v>
+      </c>
+      <c r="G7" s="10">
+        <v>1578.9</v>
+      </c>
+      <c r="H7" s="12">
+        <v>61.6</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -2267,25 +2268,25 @@
         <v>21</v>
       </c>
       <c r="B8" s="10">
-        <v>220</v>
+        <v>166</v>
       </c>
       <c r="C8" s="11">
-        <v>0.853</v>
+        <v>0.84</v>
       </c>
       <c r="D8" s="11">
-        <v>0.974</v>
+        <v>0.968</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="F8" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="H8" s="12" t="s">
-        <v>9</v>
+      <c r="F8" s="10">
+        <v>360</v>
+      </c>
+      <c r="G8" s="10">
+        <v>958.1</v>
+      </c>
+      <c r="H8" s="12">
+        <v>40.4</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -2319,25 +2320,25 @@
         <v>25</v>
       </c>
       <c r="B10" s="10">
-        <v>59</v>
+        <v>118</v>
       </c>
       <c r="C10" s="11">
-        <v>0.82</v>
+        <v>0.836</v>
       </c>
       <c r="D10" s="11">
-        <v>0.958</v>
+        <v>0.967</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="F10" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="H10" s="12" t="s">
-        <v>9</v>
+      <c r="F10" s="10">
+        <v>312</v>
+      </c>
+      <c r="G10" s="10">
+        <v>579.2</v>
+      </c>
+      <c r="H10" s="12">
+        <v>25.3</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -2345,25 +2346,25 @@
         <v>27</v>
       </c>
       <c r="B11" s="10">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="C11" s="11">
-        <v>0.805</v>
+        <v>0.829</v>
       </c>
       <c r="D11" s="11">
-        <v>0.951</v>
+        <v>0.964</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="F11" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="H11" s="12" t="s">
-        <v>9</v>
+      <c r="F11" s="10">
+        <v>258</v>
+      </c>
+      <c r="G11" s="10">
+        <v>308.3</v>
+      </c>
+      <c r="H11" s="12">
+        <v>15.1</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -2371,25 +2372,25 @@
         <v>29</v>
       </c>
       <c r="B12" s="10">
-        <v>34</v>
+        <v>343</v>
       </c>
       <c r="C12" s="11">
-        <v>0.798</v>
+        <v>0.825</v>
       </c>
       <c r="D12" s="11">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F12" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="H12" s="12" t="s">
-        <v>9</v>
+      <c r="F12" s="10">
+        <v>533</v>
+      </c>
+      <c r="G12" s="10">
+        <v>344.5</v>
+      </c>
+      <c r="H12" s="12">
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -2397,13 +2398,13 @@
         <v>31</v>
       </c>
       <c r="B13" s="10">
-        <v>29</v>
+        <v>192.29</v>
       </c>
       <c r="C13" s="11">
-        <v>0.787</v>
-      </c>
-      <c r="D13" s="11">
-        <v>0.943</v>
+        <v>0.823</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>9</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>32</v>
@@ -2423,25 +2424,25 @@
         <v>33</v>
       </c>
       <c r="B14" s="10">
-        <v>256</v>
+        <v>59</v>
       </c>
       <c r="C14" s="11">
-        <v>0.843</v>
+        <v>0.82</v>
       </c>
       <c r="D14" s="11">
-        <v>0.97</v>
+        <v>0.958</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="F14" s="10">
-        <v>438</v>
-      </c>
-      <c r="G14" s="10">
-        <v>1578.9</v>
-      </c>
-      <c r="H14" s="12">
-        <v>61.6</v>
+      <c r="F14" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -2449,25 +2450,25 @@
         <v>35</v>
       </c>
       <c r="B15" s="10">
-        <v>166</v>
+        <v>48</v>
       </c>
       <c r="C15" s="11">
-        <v>0.84</v>
+        <v>0.816</v>
       </c>
       <c r="D15" s="11">
-        <v>0.968</v>
+        <v>0.957</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>36</v>
       </c>
       <c r="F15" s="10">
-        <v>360</v>
+        <v>210</v>
       </c>
       <c r="G15" s="10">
-        <v>958.1</v>
+        <v>140</v>
       </c>
       <c r="H15" s="12">
-        <v>40.4</v>
+        <v>8.8</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -2475,25 +2476,25 @@
         <v>37</v>
       </c>
       <c r="B16" s="10">
-        <v>118</v>
+        <v>109.42</v>
       </c>
       <c r="C16" s="11">
-        <v>0.836</v>
-      </c>
-      <c r="D16" s="11">
-        <v>0.967</v>
+        <v>0.813</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>9</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="F16" s="10">
-        <v>312</v>
-      </c>
-      <c r="G16" s="10">
-        <v>579.2</v>
-      </c>
-      <c r="H16" s="12">
-        <v>25.3</v>
+      <c r="F16" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="H16" s="12" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -2501,25 +2502,25 @@
         <v>39</v>
       </c>
       <c r="B17" s="10">
-        <v>343</v>
+        <v>42</v>
       </c>
       <c r="C17" s="11">
-        <v>0.825</v>
+        <v>0.805</v>
       </c>
       <c r="D17" s="11">
-        <v>0.96</v>
+        <v>0.951</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="F17" s="10">
-        <v>533</v>
-      </c>
-      <c r="G17" s="10">
-        <v>344.5</v>
-      </c>
-      <c r="H17" s="12">
-        <v>20</v>
+      <c r="F17" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="H17" s="12" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -2527,51 +2528,51 @@
         <v>41</v>
       </c>
       <c r="B18" s="10">
-        <v>75</v>
+        <v>215</v>
       </c>
       <c r="C18" s="11">
-        <v>0.829</v>
+        <v>0.803</v>
       </c>
       <c r="D18" s="11">
-        <v>0.964</v>
+        <v>0.953</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>42</v>
       </c>
       <c r="F18" s="10">
-        <v>258</v>
+        <v>449</v>
       </c>
       <c r="G18" s="10">
-        <v>308.3</v>
+        <v>130.2</v>
       </c>
       <c r="H18" s="12">
-        <v>15.1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="9" t="s">
+      <c r="A19" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B19" s="10">
-        <v>48</v>
-      </c>
-      <c r="C19" s="11">
-        <v>0.816</v>
-      </c>
-      <c r="D19" s="11">
-        <v>0.957</v>
-      </c>
-      <c r="E19" s="10" t="s">
+      <c r="B19" s="14">
+        <v>36</v>
+      </c>
+      <c r="C19" s="15">
+        <v>0.801</v>
+      </c>
+      <c r="D19" s="15">
+        <v>0.949</v>
+      </c>
+      <c r="E19" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F19" s="10">
-        <v>210</v>
-      </c>
-      <c r="G19" s="10">
-        <v>140</v>
-      </c>
-      <c r="H19" s="12">
-        <v>8.8</v>
+      <c r="F19" s="14">
+        <v>186</v>
+      </c>
+      <c r="G19" s="14">
+        <v>80.8</v>
+      </c>
+      <c r="H19" s="16">
+        <v>6.5</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -2579,25 +2580,25 @@
         <v>45</v>
       </c>
       <c r="B20" s="10">
-        <v>215</v>
+        <v>34</v>
       </c>
       <c r="C20" s="11">
-        <v>0.803</v>
+        <v>0.798</v>
       </c>
       <c r="D20" s="11">
-        <v>0.953</v>
+        <v>0.95</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="F20" s="10">
-        <v>449</v>
-      </c>
-      <c r="G20" s="10">
-        <v>130.2</v>
-      </c>
-      <c r="H20" s="12">
-        <v>10</v>
+      <c r="F20" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="H20" s="12" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -2605,25 +2606,25 @@
         <v>47</v>
       </c>
       <c r="B21" s="10">
-        <v>232</v>
+        <v>31</v>
       </c>
       <c r="C21" s="11">
-        <v>0.766</v>
+        <v>0.791</v>
       </c>
       <c r="D21" s="11">
-        <v>0.931</v>
+        <v>0.944</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>48</v>
       </c>
       <c r="F21" s="10">
-        <v>311</v>
+        <v>186</v>
       </c>
       <c r="G21" s="10">
-        <v>127.4</v>
+        <v>60.2</v>
       </c>
       <c r="H21" s="12">
-        <v>6.5</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -2631,51 +2632,51 @@
         <v>49</v>
       </c>
       <c r="B22" s="10">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="C22" s="11">
-        <v>0.773</v>
+        <v>0.79</v>
       </c>
       <c r="D22" s="11">
-        <v>0.936</v>
+        <v>0.945</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>50</v>
       </c>
       <c r="F22" s="10">
-        <v>402</v>
+        <v>81</v>
       </c>
       <c r="G22" s="10">
-        <v>127.2</v>
+        <v>109.4</v>
       </c>
       <c r="H22" s="12">
-        <v>6.7</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="13" t="s">
+      <c r="A23" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B23" s="14">
-        <v>88</v>
-      </c>
-      <c r="C23" s="15">
-        <v>0.79</v>
-      </c>
-      <c r="D23" s="15">
-        <v>0.945</v>
-      </c>
-      <c r="E23" s="14" t="s">
+      <c r="B23" s="10">
+        <v>29</v>
+      </c>
+      <c r="C23" s="11">
+        <v>0.787</v>
+      </c>
+      <c r="D23" s="11">
+        <v>0.943</v>
+      </c>
+      <c r="E23" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="F23" s="14">
-        <v>81</v>
-      </c>
-      <c r="G23" s="14">
-        <v>109.4</v>
-      </c>
-      <c r="H23" s="16">
-        <v>8.1</v>
+      <c r="F23" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="H23" s="12" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -2692,7 +2693,7 @@
         <v>0.942</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F24" s="10">
         <v>307</v>
@@ -2705,133 +2706,133 @@
       </c>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="B25" s="10">
-        <v>57</v>
-      </c>
-      <c r="C25" s="11">
-        <v>0.762</v>
-      </c>
-      <c r="D25" s="11">
-        <v>0.932</v>
-      </c>
-      <c r="E25" s="10" t="s">
+      <c r="A25" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="F25" s="10">
-        <v>338</v>
-      </c>
-      <c r="G25" s="10">
-        <v>96.4</v>
-      </c>
-      <c r="H25" s="12">
-        <v>6.3</v>
+      <c r="B25" s="18">
+        <v>92</v>
+      </c>
+      <c r="C25" s="19">
+        <v>0.779</v>
+      </c>
+      <c r="D25" s="19">
+        <v>0.937</v>
+      </c>
+      <c r="E25" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="F25" s="18">
+        <v>189</v>
+      </c>
+      <c r="G25" s="18">
+        <v>42.2</v>
+      </c>
+      <c r="H25" s="20">
+        <v>6.9</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B26" s="10">
-        <v>171</v>
+        <v>80</v>
       </c>
       <c r="C26" s="11">
-        <v>0.764</v>
+        <v>0.773</v>
       </c>
       <c r="D26" s="11">
-        <v>0.928</v>
+        <v>0.936</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F26" s="10">
-        <v>209</v>
+        <v>402</v>
       </c>
       <c r="G26" s="10">
-        <v>89.6</v>
+        <v>127.2</v>
       </c>
       <c r="H26" s="12">
-        <v>5.2</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B27" s="10">
-        <v>549</v>
+        <v>171</v>
       </c>
       <c r="C27" s="11">
-        <v>0.713</v>
+        <v>0.772</v>
       </c>
       <c r="D27" s="11">
-        <v>0.9</v>
+        <v>0.938</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F27" s="10">
-        <v>19</v>
+        <v>205</v>
       </c>
       <c r="G27" s="10">
-        <v>84.8</v>
+        <v>72.7</v>
       </c>
       <c r="H27" s="12">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="B28" s="18">
-        <v>36</v>
-      </c>
-      <c r="C28" s="19">
-        <v>0.801</v>
-      </c>
-      <c r="D28" s="19">
-        <v>0.949</v>
-      </c>
-      <c r="E28" s="18" t="s">
+      <c r="A28" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="F28" s="18">
-        <v>186</v>
-      </c>
-      <c r="G28" s="18">
-        <v>80.8</v>
-      </c>
-      <c r="H28" s="20">
-        <v>6.5</v>
+      <c r="B28" s="10">
+        <v>29</v>
+      </c>
+      <c r="C28" s="11">
+        <v>0.771</v>
+      </c>
+      <c r="D28" s="11">
+        <v>0.933</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="F28" s="10">
+        <v>132</v>
+      </c>
+      <c r="G28" s="10">
+        <v>46</v>
+      </c>
+      <c r="H28" s="12">
+        <v>4.9</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B29" s="10">
-        <v>33</v>
+        <v>232</v>
       </c>
       <c r="C29" s="11">
-        <v>0.75</v>
+        <v>0.766</v>
       </c>
       <c r="D29" s="11">
-        <v>0.923</v>
+        <v>0.931</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F29" s="10">
-        <v>242</v>
+        <v>311</v>
       </c>
       <c r="G29" s="10">
-        <v>77.1</v>
+        <v>127.4</v>
       </c>
       <c r="H29" s="12">
-        <v>5.4</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -2842,22 +2843,22 @@
         <v>171</v>
       </c>
       <c r="C30" s="11">
-        <v>0.772</v>
+        <v>0.764</v>
       </c>
       <c r="D30" s="11">
-        <v>0.938</v>
+        <v>0.928</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F30" s="10">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="G30" s="10">
-        <v>72.7</v>
+        <v>89.6</v>
       </c>
       <c r="H30" s="12">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -2865,25 +2866,25 @@
         <v>65</v>
       </c>
       <c r="B31" s="10">
-        <v>528</v>
+        <v>57</v>
       </c>
       <c r="C31" s="11">
-        <v>0.713</v>
+        <v>0.762</v>
       </c>
       <c r="D31" s="11">
-        <v>0.901</v>
+        <v>0.932</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>66</v>
       </c>
       <c r="F31" s="10">
-        <v>16</v>
+        <v>338</v>
       </c>
       <c r="G31" s="10">
-        <v>69.5</v>
+        <v>96.4</v>
       </c>
       <c r="H31" s="12">
-        <v>4.2</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -2891,25 +2892,25 @@
         <v>67</v>
       </c>
       <c r="B32" s="10">
-        <v>31</v>
+        <v>98</v>
       </c>
       <c r="C32" s="11">
-        <v>0.791</v>
+        <v>0.76</v>
       </c>
       <c r="D32" s="11">
-        <v>0.944</v>
+        <v>0.93</v>
       </c>
       <c r="E32" s="10" t="s">
         <v>68</v>
       </c>
       <c r="F32" s="10">
-        <v>186</v>
+        <v>103</v>
       </c>
       <c r="G32" s="10">
-        <v>60.2</v>
+        <v>45.6</v>
       </c>
       <c r="H32" s="12">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -2917,25 +2918,25 @@
         <v>69</v>
       </c>
       <c r="B33" s="10">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="C33" s="11">
-        <v>0.749</v>
+        <v>0.75</v>
       </c>
       <c r="D33" s="11">
-        <v>0.921</v>
+        <v>0.923</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>70</v>
       </c>
       <c r="F33" s="10">
-        <v>107</v>
+        <v>242</v>
       </c>
       <c r="G33" s="10">
-        <v>58.2</v>
+        <v>77.1</v>
       </c>
       <c r="H33" s="12">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -2943,103 +2944,103 @@
         <v>71</v>
       </c>
       <c r="B34" s="10">
-        <v>29</v>
+        <v>98</v>
       </c>
       <c r="C34" s="11">
-        <v>0.771</v>
+        <v>0.749</v>
       </c>
       <c r="D34" s="11">
-        <v>0.933</v>
+        <v>0.921</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F34" s="10">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="G34" s="10">
-        <v>46</v>
+        <v>58.2</v>
       </c>
       <c r="H34" s="12">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="B35" s="10">
+        <v>23</v>
+      </c>
+      <c r="C35" s="11">
+        <v>0.744</v>
+      </c>
+      <c r="D35" s="11">
+        <v>0.919</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="F35" s="10">
+        <v>389</v>
+      </c>
+      <c r="G35" s="10">
+        <v>27</v>
+      </c>
+      <c r="H35" s="12">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="B35" s="10">
-        <v>98</v>
-      </c>
-      <c r="C35" s="11">
-        <v>0.76</v>
-      </c>
-      <c r="D35" s="11">
-        <v>0.93</v>
-      </c>
-      <c r="E35" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="F35" s="10">
-        <v>103</v>
-      </c>
-      <c r="G35" s="10">
-        <v>45.6</v>
-      </c>
-      <c r="H35" s="12">
+      <c r="B36" s="10">
+        <v>549</v>
+      </c>
+      <c r="C36" s="11">
+        <v>0.713</v>
+      </c>
+      <c r="D36" s="11">
+        <v>0.9</v>
+      </c>
+      <c r="E36" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="F36" s="10">
+        <v>19</v>
+      </c>
+      <c r="G36" s="10">
+        <v>84.8</v>
+      </c>
+      <c r="H36" s="12">
         <v>4.4</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8">
-      <c r="A36" s="21" t="s">
-        <v>74</v>
-      </c>
-      <c r="B36" s="22">
-        <v>92</v>
-      </c>
-      <c r="C36" s="23">
-        <v>0.779</v>
-      </c>
-      <c r="D36" s="23">
-        <v>0.937</v>
-      </c>
-      <c r="E36" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="F36" s="22">
-        <v>189</v>
-      </c>
-      <c r="G36" s="22">
-        <v>42.2</v>
-      </c>
-      <c r="H36" s="24">
-        <v>6.9</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="B37" s="10">
+        <v>528</v>
+      </c>
+      <c r="C37" s="11">
+        <v>0.713</v>
+      </c>
+      <c r="D37" s="11">
+        <v>0.901</v>
+      </c>
+      <c r="E37" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="B37" s="10">
-        <v>23</v>
-      </c>
-      <c r="C37" s="11">
-        <v>0.744</v>
-      </c>
-      <c r="D37" s="11">
-        <v>0.919</v>
-      </c>
-      <c r="E37" s="10" t="s">
-        <v>72</v>
-      </c>
       <c r="F37" s="10">
-        <v>389</v>
+        <v>16</v>
       </c>
       <c r="G37" s="10">
-        <v>27</v>
+        <v>69.5</v>
       </c>
       <c r="H37" s="12">
-        <v>6.7</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -3068,73 +3069,73 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="39" ht="14.25" spans="1:8">
-      <c r="A39" s="25" t="s">
+    <row r="39" spans="1:8">
+      <c r="A39" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="B39" s="26">
+      <c r="B39" s="22">
         <v>16</v>
       </c>
-      <c r="C39" s="27">
+      <c r="C39" s="23">
         <v>0.704</v>
       </c>
-      <c r="D39" s="27">
+      <c r="D39" s="23">
         <v>0.895</v>
       </c>
-      <c r="E39" s="26" t="s">
+      <c r="E39" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="F39" s="26">
+      <c r="F39" s="22">
         <v>55</v>
       </c>
-      <c r="G39" s="26">
+      <c r="G39" s="22">
         <v>22.6</v>
       </c>
-      <c r="H39" s="28">
+      <c r="H39" s="24">
         <v>3.4</v>
       </c>
     </row>
   </sheetData>
   <sortState ref="A2:H39">
-    <sortCondition ref="G2" descending="1"/>
+    <sortCondition ref="C2" descending="1"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="A23" r:id="rId1" display="Xception" tooltip="https://keras.io/api/applications/xception"/>
-    <hyperlink ref="A31" r:id="rId2" location="vgg16-function" display="VGG16"/>
-    <hyperlink ref="A27" r:id="rId2" location="vgg19-function" display="VGG19"/>
-    <hyperlink ref="A33" r:id="rId3" location="resnet50-function" display="ResNet50"/>
-    <hyperlink ref="A35" r:id="rId3" location="resnet50v2-function" display="ResNet50V2"/>
-    <hyperlink ref="A26" r:id="rId3" location="resnet101-function" display="ResNet101"/>
-    <hyperlink ref="A30" r:id="rId3" location="resnet101v2-function" display="ResNet101V2"/>
-    <hyperlink ref="A21" r:id="rId3" location="resnet152-function" display="ResNet152"/>
+    <hyperlink ref="A22" r:id="rId1" display="Xception" tooltip="https://keras.io/api/applications/xception"/>
+    <hyperlink ref="A37" r:id="rId2" location="vgg16-function" display="VGG16"/>
+    <hyperlink ref="A36" r:id="rId2" location="vgg19-function" display="VGG19"/>
+    <hyperlink ref="A34" r:id="rId3" location="resnet50-function" display="ResNet50"/>
+    <hyperlink ref="A32" r:id="rId3" location="resnet50v2-function" display="ResNet50V2"/>
+    <hyperlink ref="A30" r:id="rId3" location="resnet101-function" display="ResNet101"/>
+    <hyperlink ref="A27" r:id="rId3" location="resnet101v2-function" display="ResNet101V2"/>
+    <hyperlink ref="A29" r:id="rId3" location="resnet152-function" display="ResNet152"/>
     <hyperlink ref="A24" r:id="rId3" location="resnet152v2-function" display="ResNet152V2"/>
-    <hyperlink ref="A36" r:id="rId4" display="InceptionV3" tooltip="https://keras.io/api/applications/inceptionv3"/>
-    <hyperlink ref="A20" r:id="rId5" display="InceptionResNetV2" tooltip="https://keras.io/api/applications/inceptionresnetv2"/>
+    <hyperlink ref="A25" r:id="rId4" display="InceptionV3" tooltip="https://keras.io/api/applications/inceptionv3"/>
+    <hyperlink ref="A18" r:id="rId5" display="InceptionResNetV2" tooltip="https://keras.io/api/applications/inceptionresnetv2"/>
     <hyperlink ref="A39" r:id="rId6" display="MobileNet" tooltip="https://keras.io/api/applications/mobilenet"/>
     <hyperlink ref="A38" r:id="rId7" location="mobilenetv2-function" display="MobileNetV2"/>
-    <hyperlink ref="A29" r:id="rId8" location="densenet121-function" display="DenseNet121"/>
-    <hyperlink ref="A25" r:id="rId8" location="densenet169-function" display="DenseNet169"/>
-    <hyperlink ref="A22" r:id="rId8" location="densenet201-function" display="DenseNet201"/>
-    <hyperlink ref="A37" r:id="rId9" location="nasnetmobile-function" display="NASNetMobile"/>
-    <hyperlink ref="A17" r:id="rId9" location="nasnetlarge-function" display="NASNetLarge"/>
-    <hyperlink ref="A34" r:id="rId10" location="efficientnetb0-function" display="EfficientNetB0"/>
-    <hyperlink ref="A32" r:id="rId10" location="efficientnetb1-function" display="EfficientNetB1"/>
-    <hyperlink ref="A28" r:id="rId10" location="efficientnetb2-function" display="EfficientNetB2"/>
-    <hyperlink ref="A19" r:id="rId10" location="efficientnetb3-function" display="EfficientNetB3"/>
-    <hyperlink ref="A18" r:id="rId10" location="efficientnetb4-function" display="EfficientNetB4"/>
-    <hyperlink ref="A16" r:id="rId10" location="efficientnetb5-function" display="EfficientNetB5"/>
-    <hyperlink ref="A15" r:id="rId10" location="efficientnetb6-function" display="EfficientNetB6"/>
-    <hyperlink ref="A14" r:id="rId10" location="efficientnetb7-function" display="EfficientNetB7"/>
-    <hyperlink ref="A13" r:id="rId11" location="efficientnetv2b0-function" display="EfficientNetV2B0"/>
-    <hyperlink ref="A12" r:id="rId11" location="efficientnetv2b1-function" display="EfficientNetV2B1"/>
-    <hyperlink ref="A11" r:id="rId11" location="efficientnetv2b2-function" display="EfficientNetV2B2"/>
-    <hyperlink ref="A10" r:id="rId11" location="efficientnetv2b3-function" display="EfficientNetV2B3"/>
+    <hyperlink ref="A33" r:id="rId8" location="densenet121-function" display="DenseNet121"/>
+    <hyperlink ref="A31" r:id="rId8" location="densenet169-function" display="DenseNet169"/>
+    <hyperlink ref="A26" r:id="rId8" location="densenet201-function" display="DenseNet201"/>
+    <hyperlink ref="A35" r:id="rId9" location="nasnetmobile-function" display="NASNetMobile"/>
+    <hyperlink ref="A12" r:id="rId9" location="nasnetlarge-function" display="NASNetLarge"/>
+    <hyperlink ref="A28" r:id="rId10" location="efficientnetb0-function" display="EfficientNetB0"/>
+    <hyperlink ref="A21" r:id="rId10" location="efficientnetb1-function" display="EfficientNetB1"/>
+    <hyperlink ref="A19" r:id="rId10" location="efficientnetb2-function" display="EfficientNetB2"/>
+    <hyperlink ref="A15" r:id="rId10" location="efficientnetb3-function" display="EfficientNetB3"/>
+    <hyperlink ref="A11" r:id="rId10" location="efficientnetb4-function" display="EfficientNetB4"/>
+    <hyperlink ref="A10" r:id="rId10" location="efficientnetb5-function" display="EfficientNetB5"/>
+    <hyperlink ref="A8" r:id="rId10" location="efficientnetb6-function" display="EfficientNetB6"/>
+    <hyperlink ref="A7" r:id="rId10" location="efficientnetb7-function" display="EfficientNetB7"/>
+    <hyperlink ref="A23" r:id="rId11" location="efficientnetv2b0-function" display="EfficientNetV2B0"/>
+    <hyperlink ref="A20" r:id="rId11" location="efficientnetv2b1-function" display="EfficientNetV2B1"/>
+    <hyperlink ref="A17" r:id="rId11" location="efficientnetv2b2-function" display="EfficientNetV2B2"/>
+    <hyperlink ref="A14" r:id="rId11" location="efficientnetv2b3-function" display="EfficientNetV2B3"/>
     <hyperlink ref="A9" r:id="rId11" location="efficientnetv2s-function" display="EfficientNetV2S"/>
-    <hyperlink ref="A8" r:id="rId11" location="efficientnetv2m-function" display="EfficientNetV2M"/>
-    <hyperlink ref="A7" r:id="rId11" location="efficientnetv2l-function" display="EfficientNetV2L"/>
-    <hyperlink ref="A6" r:id="rId12" location="convnexttiny-function" display="ConvNeXtTiny"/>
-    <hyperlink ref="A5" r:id="rId12" location="convnextsmall-function" display="ConvNeXtSmall"/>
-    <hyperlink ref="A4" r:id="rId12" location="convnextbase-function" display="ConvNeXtBase"/>
+    <hyperlink ref="A6" r:id="rId11" location="efficientnetv2m-function" display="EfficientNetV2M"/>
+    <hyperlink ref="A4" r:id="rId11" location="efficientnetv2l-function" display="EfficientNetV2L"/>
+    <hyperlink ref="A16" r:id="rId12" location="convnexttiny-function" display="ConvNeXtTiny"/>
+    <hyperlink ref="A13" r:id="rId12" location="convnextsmall-function" display="ConvNeXtSmall"/>
+    <hyperlink ref="A5" r:id="rId12" location="convnextbase-function" display="ConvNeXtBase"/>
     <hyperlink ref="A3" r:id="rId12" location="convnextlarge-function" display="ConvNeXtLarge"/>
     <hyperlink ref="A2" r:id="rId12" location="convnextxlarge-function" display="ConvNeXtXLarge"/>
   </hyperlinks>
